--- a/판매용_템플릿/_판매팩/LMS_프리미엄/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/LMS_프리미엄/08_검수시나리오.xlsx
@@ -1412,10 +1412,10 @@
         <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>브라우저 폭을 390px 로 좁혀 화면을 훑고, 360px 로 한 번 더 훑는다. ⚠ 세로 flex 로 바꾼 상자의 자식이 밀리는 것은 390px 에서는 안 보이고 360px 에서만 나온다.</v>
       </c>
       <c r="H19" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>두 폭 모두에서 가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>

--- a/판매용_템플릿/_판매팩/LMS_프리미엄/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/LMS_프리미엄/08_검수시나리오.xlsx
@@ -1572,7 +1572,7 @@
         <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
+        <v>스펙팩 7-9 의 글을 화면에 붙여 넣으면 ⑧번이 잰다(7-9-2 는 파일만 보므로 대비를 재지 않는다). ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
         <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
